--- a/hall/resources/sample/BuildingGain.xlsx
+++ b/hall/resources/sample/BuildingGain.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="13">
   <si>
     <t>id</t>
   </si>
@@ -1072,7 +1072,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="4" max="4" width="26" customWidth="1"/>
@@ -1096,7 +1096,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="2:5">
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
@@ -1121,723 +1124,723 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <f>10000+C4+B4*1000</f>
-        <v>11001</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4">
-        <v>500</v>
-      </c>
-    </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <f t="shared" ref="A5:A43" si="0">10000+C5+B5*1000</f>
-        <v>11002</v>
+        <f>10000+C5+B5*1000</f>
+        <v>11001</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>
       </c>
       <c r="E5">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <f t="shared" si="0"/>
-        <v>11003</v>
+        <f t="shared" ref="A6:A44" si="0">10000+C6+B6*1000</f>
+        <v>11002</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
       </c>
       <c r="E6">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>11004</v>
+        <v>11003</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
       </c>
       <c r="E7">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>11005</v>
+        <v>11004</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
       </c>
       <c r="E8">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
         <f t="shared" si="0"/>
-        <v>11006</v>
+        <v>11005</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
       </c>
       <c r="E9">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
         <f t="shared" si="0"/>
-        <v>11007</v>
+        <v>11006</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
       </c>
       <c r="E10">
-        <v>3500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
         <f t="shared" si="0"/>
-        <v>11008</v>
+        <v>11007</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
       </c>
       <c r="E11">
-        <v>4000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
         <f t="shared" si="0"/>
-        <v>11009</v>
+        <v>11008</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
       </c>
       <c r="E12">
-        <v>4500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
         <f t="shared" si="0"/>
-        <v>11010</v>
+        <v>11009</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
         <v>9</v>
       </c>
       <c r="E13">
-        <v>5000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
         <f t="shared" si="0"/>
-        <v>12001</v>
+        <v>11010</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E14">
-        <v>500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
         <f t="shared" si="0"/>
-        <v>12002</v>
+        <v>12001</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
       </c>
       <c r="E15">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
         <f t="shared" si="0"/>
-        <v>12003</v>
+        <v>12002</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
       </c>
       <c r="E16">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
         <f t="shared" si="0"/>
-        <v>12004</v>
+        <v>12003</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
       </c>
       <c r="E17">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
         <f t="shared" si="0"/>
-        <v>12005</v>
+        <v>12004</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
       </c>
       <c r="E18">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
         <f t="shared" si="0"/>
-        <v>12006</v>
+        <v>12005</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
       </c>
       <c r="E19">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
         <f t="shared" si="0"/>
-        <v>12007</v>
+        <v>12006</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
       </c>
       <c r="E20">
-        <v>3500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
         <f t="shared" si="0"/>
-        <v>12008</v>
+        <v>12007</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
       </c>
       <c r="E21">
-        <v>4000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
         <f t="shared" si="0"/>
-        <v>12009</v>
+        <v>12008</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
       </c>
       <c r="E22">
-        <v>4500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
         <f t="shared" si="0"/>
-        <v>12010</v>
+        <v>12009</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
       </c>
       <c r="E23">
-        <v>5000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
         <f t="shared" si="0"/>
-        <v>21001</v>
+        <v>12010</v>
       </c>
       <c r="B24">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E24">
-        <v>500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
         <f t="shared" si="0"/>
-        <v>21002</v>
+        <v>21001</v>
       </c>
       <c r="B25">
         <v>11</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
       <c r="E25">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
         <f t="shared" si="0"/>
-        <v>21003</v>
+        <v>21002</v>
       </c>
       <c r="B26">
         <v>11</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
       </c>
       <c r="E26">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
         <f t="shared" si="0"/>
-        <v>21004</v>
+        <v>21003</v>
       </c>
       <c r="B27">
         <v>11</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
       </c>
       <c r="E27">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
         <f t="shared" si="0"/>
-        <v>21005</v>
+        <v>21004</v>
       </c>
       <c r="B28">
         <v>11</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
       </c>
       <c r="E28">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
         <f t="shared" si="0"/>
-        <v>21006</v>
+        <v>21005</v>
       </c>
       <c r="B29">
         <v>11</v>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
       </c>
       <c r="E29">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
         <f t="shared" si="0"/>
-        <v>21007</v>
+        <v>21006</v>
       </c>
       <c r="B30">
         <v>11</v>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30">
-        <v>3500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
         <f t="shared" si="0"/>
-        <v>21008</v>
+        <v>21007</v>
       </c>
       <c r="B31">
         <v>11</v>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
       </c>
       <c r="E31">
-        <v>4000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
         <f t="shared" si="0"/>
-        <v>21009</v>
+        <v>21008</v>
       </c>
       <c r="B32">
         <v>11</v>
       </c>
       <c r="C32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
       </c>
       <c r="E32">
-        <v>4500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
         <f t="shared" si="0"/>
-        <v>21010</v>
+        <v>21009</v>
       </c>
       <c r="B33">
         <v>11</v>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
       </c>
       <c r="E33">
-        <v>5000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
         <f t="shared" si="0"/>
-        <v>22001</v>
+        <v>21010</v>
       </c>
       <c r="B34">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E34">
-        <v>500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
         <f t="shared" si="0"/>
-        <v>22002</v>
+        <v>22001</v>
       </c>
       <c r="B35">
         <v>12</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="s">
         <v>12</v>
       </c>
       <c r="E35">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
         <f t="shared" si="0"/>
-        <v>22003</v>
+        <v>22002</v>
       </c>
       <c r="B36">
         <v>12</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" t="s">
         <v>12</v>
       </c>
       <c r="E36">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
         <f t="shared" si="0"/>
-        <v>22004</v>
+        <v>22003</v>
       </c>
       <c r="B37">
         <v>12</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
       <c r="E37">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
         <f t="shared" si="0"/>
-        <v>22005</v>
+        <v>22004</v>
       </c>
       <c r="B38">
         <v>12</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
       <c r="E38">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
         <f t="shared" si="0"/>
-        <v>22006</v>
+        <v>22005</v>
       </c>
       <c r="B39">
         <v>12</v>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D39" t="s">
         <v>12</v>
       </c>
       <c r="E39">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
         <f t="shared" si="0"/>
-        <v>22007</v>
+        <v>22006</v>
       </c>
       <c r="B40">
         <v>12</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
       </c>
       <c r="E40">
-        <v>3500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
         <f t="shared" si="0"/>
-        <v>22008</v>
+        <v>22007</v>
       </c>
       <c r="B41">
         <v>12</v>
       </c>
       <c r="C41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D41" t="s">
         <v>12</v>
       </c>
       <c r="E41">
-        <v>4000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
         <f t="shared" si="0"/>
-        <v>22009</v>
+        <v>22008</v>
       </c>
       <c r="B42">
         <v>12</v>
       </c>
       <c r="C42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42" t="s">
         <v>12</v>
       </c>
       <c r="E42">
-        <v>4500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
         <f t="shared" si="0"/>
+        <v>22009</v>
+      </c>
+      <c r="B43">
+        <v>12</v>
+      </c>
+      <c r="C43">
+        <v>9</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <f t="shared" si="0"/>
         <v>22010</v>
       </c>
-      <c r="B43">
-        <v>12</v>
-      </c>
-      <c r="C43">
+      <c r="B44">
+        <v>12</v>
+      </c>
+      <c r="C44">
         <v>10</v>
       </c>
-      <c r="D43" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43">
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44">
         <v>5000</v>
       </c>
     </row>

--- a/hall/resources/sample/BuildingGain.xlsx
+++ b/hall/resources/sample/BuildingGain.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="14">
   <si>
     <t>id</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>addvalue</t>
+  </si>
+  <si>
+    <t>langId</t>
   </si>
   <si>
     <t>增加收益万分比+</t>
@@ -1072,8 +1075,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="13.625" customWidth="1"/>
@@ -1096,7 +1099,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1109,8 +1112,11 @@
       <c r="E2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1123,8 +1129,11 @@
       <c r="E3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <f>10000+C5+B5*1000</f>
         <v>11001</v>
@@ -1136,13 +1145,16 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>500</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <f t="shared" ref="A6:A44" si="0">10000+C6+B6*1000</f>
         <v>11002</v>
@@ -1154,13 +1166,16 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>1000</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>11003</v>
@@ -1172,13 +1187,16 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7">
         <v>1500</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>11004</v>
@@ -1190,13 +1208,16 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>2000</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>11005</v>
@@ -1208,13 +1229,16 @@
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9">
         <v>2500</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>11006</v>
@@ -1226,13 +1250,16 @@
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10">
         <v>3000</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>11007</v>
@@ -1244,13 +1271,16 @@
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11">
         <v>3500</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11008</v>
@@ -1262,13 +1292,16 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12">
         <v>4000</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>11009</v>
@@ -1280,13 +1313,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13">
         <v>4500</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>11010</v>
@@ -1298,13 +1334,16 @@
         <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14">
         <v>5000</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>12001</v>
@@ -1316,13 +1355,16 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15">
         <v>500</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>12002</v>
@@ -1334,13 +1376,16 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16">
         <v>1000</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>12003</v>
@@ -1352,13 +1397,16 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17">
         <v>1500</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>12004</v>
@@ -1370,13 +1418,16 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18">
         <v>2000</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>12005</v>
@@ -1388,13 +1439,16 @@
         <v>5</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19">
         <v>2500</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>12006</v>
@@ -1406,13 +1460,16 @@
         <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20">
         <v>3000</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>12007</v>
@@ -1424,13 +1481,16 @@
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21">
         <v>3500</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>12008</v>
@@ -1442,13 +1502,16 @@
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22">
         <v>4000</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>12009</v>
@@ -1460,13 +1523,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23">
         <v>4500</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>12010</v>
@@ -1478,13 +1544,16 @@
         <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24">
         <v>5000</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>21001</v>
@@ -1496,13 +1565,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E25">
         <v>500</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>21002</v>
@@ -1514,13 +1586,16 @@
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E26">
         <v>1000</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>21003</v>
@@ -1532,13 +1607,16 @@
         <v>3</v>
       </c>
       <c r="D27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E27">
         <v>1500</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>21004</v>
@@ -1550,13 +1628,16 @@
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E28">
         <v>2000</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>21005</v>
@@ -1568,13 +1649,16 @@
         <v>5</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E29">
         <v>2500</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>21006</v>
@@ -1586,13 +1670,16 @@
         <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E30">
         <v>3000</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>21007</v>
@@ -1604,13 +1691,16 @@
         <v>7</v>
       </c>
       <c r="D31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31">
         <v>3500</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>21008</v>
@@ -1622,13 +1712,16 @@
         <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E32">
         <v>4000</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="F32">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>21009</v>
@@ -1640,13 +1733,16 @@
         <v>9</v>
       </c>
       <c r="D33" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E33">
         <v>4500</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="F33">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>21010</v>
@@ -1658,13 +1754,16 @@
         <v>10</v>
       </c>
       <c r="D34" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E34">
         <v>5000</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="F34">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>22001</v>
@@ -1676,13 +1775,16 @@
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E35">
         <v>500</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="F35">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>22002</v>
@@ -1694,13 +1796,16 @@
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E36">
         <v>1000</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="F36">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>22003</v>
@@ -1712,13 +1817,16 @@
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E37">
         <v>1500</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="F37">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>22004</v>
@@ -1730,13 +1838,16 @@
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E38">
         <v>2000</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="F38">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>22005</v>
@@ -1748,13 +1859,16 @@
         <v>5</v>
       </c>
       <c r="D39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E39">
         <v>2500</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="F39">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>22006</v>
@@ -1766,13 +1880,16 @@
         <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E40">
         <v>3000</v>
       </c>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="F40">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>22007</v>
@@ -1784,13 +1901,16 @@
         <v>7</v>
       </c>
       <c r="D41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E41">
         <v>3500</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="F41">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>22008</v>
@@ -1802,13 +1922,16 @@
         <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E42">
         <v>4000</v>
       </c>
-    </row>
-    <row r="43" spans="1:5">
+      <c r="F42">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>22009</v>
@@ -1820,13 +1943,16 @@
         <v>9</v>
       </c>
       <c r="D43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E43">
         <v>4500</v>
       </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="F43">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>22010</v>
@@ -1838,10 +1964,13 @@
         <v>10</v>
       </c>
       <c r="D44" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E44">
         <v>5000</v>
+      </c>
+      <c r="F44">
+        <v>47055</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/BuildingGain.xlsx
+++ b/hall/resources/sample/BuildingGain.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingGain" sheetId="6" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="14">
   <si>
     <t>id</t>
   </si>
@@ -1075,14 +1075,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>10</v>
       </c>
       <c r="E5">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="F5">
         <v>47054</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <f t="shared" ref="A6:A44" si="0">10000+C6+B6*1000</f>
+        <f>10000+C6+B6*1000</f>
         <v>11002</v>
       </c>
       <c r="B6">
@@ -1169,7 +1169,7 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F6">
         <v>47054</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <f t="shared" si="0"/>
+        <f>10000+C7+B7*1000</f>
         <v>11003</v>
       </c>
       <c r="B7">
@@ -1190,7 +1190,7 @@
         <v>10</v>
       </c>
       <c r="E7">
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="F7">
         <v>47054</v>
@@ -1198,7 +1198,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <f t="shared" si="0"/>
+        <f>10000+C8+B8*1000</f>
         <v>11004</v>
       </c>
       <c r="B8">
@@ -1211,7 +1211,7 @@
         <v>10</v>
       </c>
       <c r="E8">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F8">
         <v>47054</v>
@@ -1219,7 +1219,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <f t="shared" si="0"/>
+        <f>10000+C9+B9*1000</f>
         <v>11005</v>
       </c>
       <c r="B9">
@@ -1232,7 +1232,7 @@
         <v>10</v>
       </c>
       <c r="E9">
-        <v>2500</v>
+        <v>1250</v>
       </c>
       <c r="F9">
         <v>47054</v>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <f t="shared" si="0"/>
+        <f>10000+C10+B10*1000</f>
         <v>11006</v>
       </c>
       <c r="B10">
@@ -1253,7 +1253,7 @@
         <v>10</v>
       </c>
       <c r="E10">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="F10">
         <v>47054</v>
@@ -1261,7 +1261,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <f t="shared" si="0"/>
+        <f>10000+C11+B11*1000</f>
         <v>11007</v>
       </c>
       <c r="B11">
@@ -1274,7 +1274,7 @@
         <v>10</v>
       </c>
       <c r="E11">
-        <v>3500</v>
+        <v>1750</v>
       </c>
       <c r="F11">
         <v>47054</v>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <f t="shared" si="0"/>
+        <f>10000+C12+B12*1000</f>
         <v>11008</v>
       </c>
       <c r="B12">
@@ -1295,7 +1295,7 @@
         <v>10</v>
       </c>
       <c r="E12">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="F12">
         <v>47054</v>
@@ -1303,7 +1303,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <f t="shared" si="0"/>
+        <f>10000+C13+B13*1000</f>
         <v>11009</v>
       </c>
       <c r="B13">
@@ -1316,7 +1316,7 @@
         <v>10</v>
       </c>
       <c r="E13">
-        <v>4500</v>
+        <v>2250</v>
       </c>
       <c r="F13">
         <v>47054</v>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <f t="shared" si="0"/>
+        <f>10000+C14+B14*1000</f>
         <v>11010</v>
       </c>
       <c r="B14">
@@ -1337,7 +1337,7 @@
         <v>10</v>
       </c>
       <c r="E14">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="F14">
         <v>47054</v>
@@ -1345,631 +1345,1051 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <f t="shared" si="0"/>
-        <v>12001</v>
+        <f t="shared" ref="A15:A24" si="0">10000+C15+B15*1000</f>
+        <v>11011</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>500</v>
+        <v>2750</v>
       </c>
       <c r="F15">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
         <f t="shared" si="0"/>
-        <v>12002</v>
+        <v>11012</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F16">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
         <f t="shared" si="0"/>
-        <v>12003</v>
+        <v>11013</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17">
-        <v>1500</v>
+        <v>3250</v>
       </c>
       <c r="F17">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
         <f t="shared" si="0"/>
-        <v>12004</v>
+        <v>11014</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E18">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="F18">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
         <f t="shared" si="0"/>
-        <v>12005</v>
+        <v>11015</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19">
-        <v>2500</v>
+        <v>3750</v>
       </c>
       <c r="F19">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
         <f t="shared" si="0"/>
-        <v>12006</v>
+        <v>11016</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E20">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="F20">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
         <f t="shared" si="0"/>
-        <v>12007</v>
+        <v>11017</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E21">
-        <v>3500</v>
+        <v>4250</v>
       </c>
       <c r="F21">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
         <f t="shared" si="0"/>
-        <v>12008</v>
+        <v>11018</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E22">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="F22">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
         <f t="shared" si="0"/>
-        <v>12009</v>
+        <v>11019</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E23">
-        <v>4500</v>
+        <v>4750</v>
       </c>
       <c r="F23">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
         <f t="shared" si="0"/>
-        <v>12010</v>
+        <v>11020</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24">
+        <v>20</v>
+      </c>
+      <c r="D24" t="s">
         <v>10</v>
-      </c>
-      <c r="D24" t="s">
-        <v>11</v>
       </c>
       <c r="E24">
         <v>5000</v>
       </c>
       <c r="F24">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <f t="shared" si="0"/>
-        <v>21001</v>
+        <f t="shared" ref="A25:A54" si="1">10000+C25+B25*1000</f>
+        <v>12001</v>
       </c>
       <c r="B25">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25">
         <v>500</v>
       </c>
       <c r="F25">
-        <v>47054</v>
+        <v>47055</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <f t="shared" si="0"/>
-        <v>21002</v>
+        <f t="shared" si="1"/>
+        <v>12002</v>
       </c>
       <c r="B26">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E26">
         <v>1000</v>
       </c>
       <c r="F26">
-        <v>47054</v>
+        <v>47055</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <f t="shared" si="0"/>
-        <v>21003</v>
+        <f t="shared" si="1"/>
+        <v>12003</v>
       </c>
       <c r="B27">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <v>3</v>
       </c>
       <c r="D27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E27">
         <v>1500</v>
       </c>
       <c r="F27">
-        <v>47054</v>
+        <v>47055</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <f t="shared" si="0"/>
-        <v>21004</v>
+        <f t="shared" si="1"/>
+        <v>12004</v>
       </c>
       <c r="B28">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E28">
         <v>2000</v>
       </c>
       <c r="F28">
-        <v>47054</v>
+        <v>47055</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <f t="shared" si="0"/>
-        <v>21005</v>
+        <f t="shared" si="1"/>
+        <v>12005</v>
       </c>
       <c r="B29">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C29">
         <v>5</v>
       </c>
       <c r="D29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E29">
         <v>2500</v>
       </c>
       <c r="F29">
-        <v>47054</v>
+        <v>47055</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <f t="shared" si="0"/>
-        <v>21006</v>
+        <f t="shared" si="1"/>
+        <v>12006</v>
       </c>
       <c r="B30">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C30">
         <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E30">
         <v>3000</v>
       </c>
       <c r="F30">
-        <v>47054</v>
+        <v>47055</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <f t="shared" si="0"/>
-        <v>21007</v>
+        <f t="shared" si="1"/>
+        <v>12007</v>
       </c>
       <c r="B31">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C31">
         <v>7</v>
       </c>
       <c r="D31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E31">
         <v>3500</v>
       </c>
       <c r="F31">
-        <v>47054</v>
+        <v>47055</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <f t="shared" si="0"/>
-        <v>21008</v>
+        <f t="shared" si="1"/>
+        <v>12008</v>
       </c>
       <c r="B32">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C32">
         <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E32">
         <v>4000</v>
       </c>
       <c r="F32">
-        <v>47054</v>
+        <v>47055</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <f t="shared" si="0"/>
-        <v>21009</v>
+        <f t="shared" si="1"/>
+        <v>12009</v>
       </c>
       <c r="B33">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C33">
         <v>9</v>
       </c>
       <c r="D33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E33">
         <v>4500</v>
       </c>
       <c r="F33">
-        <v>47054</v>
+        <v>47055</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <f t="shared" si="0"/>
-        <v>21010</v>
+        <f t="shared" si="1"/>
+        <v>12010</v>
       </c>
       <c r="B34">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C34">
         <v>10</v>
       </c>
       <c r="D34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E34">
         <v>5000</v>
       </c>
       <c r="F34">
-        <v>47054</v>
+        <v>47055</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <f t="shared" si="0"/>
-        <v>22001</v>
+        <f t="shared" si="1"/>
+        <v>21001</v>
       </c>
       <c r="B35">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E35">
         <v>500</v>
       </c>
       <c r="F35">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <f t="shared" si="0"/>
-        <v>22002</v>
+        <f t="shared" si="1"/>
+        <v>21002</v>
       </c>
       <c r="B36">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C36">
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E36">
         <v>1000</v>
       </c>
       <c r="F36">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <f t="shared" si="0"/>
-        <v>22003</v>
+        <f t="shared" si="1"/>
+        <v>21003</v>
       </c>
       <c r="B37">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E37">
         <v>1500</v>
       </c>
       <c r="F37">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <f t="shared" si="0"/>
-        <v>22004</v>
+        <f t="shared" si="1"/>
+        <v>21004</v>
       </c>
       <c r="B38">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C38">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E38">
         <v>2000</v>
       </c>
       <c r="F38">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <f t="shared" si="0"/>
-        <v>22005</v>
+        <f t="shared" si="1"/>
+        <v>21005</v>
       </c>
       <c r="B39">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39">
         <v>5</v>
       </c>
       <c r="D39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E39">
         <v>2500</v>
       </c>
       <c r="F39">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <f t="shared" si="0"/>
-        <v>22006</v>
+        <f t="shared" si="1"/>
+        <v>21006</v>
       </c>
       <c r="B40">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C40">
         <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E40">
         <v>3000</v>
       </c>
       <c r="F40">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <f t="shared" si="0"/>
-        <v>22007</v>
+        <f t="shared" si="1"/>
+        <v>21007</v>
       </c>
       <c r="B41">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C41">
         <v>7</v>
       </c>
       <c r="D41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E41">
         <v>3500</v>
       </c>
       <c r="F41">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <f t="shared" si="0"/>
-        <v>22008</v>
+        <f t="shared" si="1"/>
+        <v>21008</v>
       </c>
       <c r="B42">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C42">
         <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E42">
         <v>4000</v>
       </c>
       <c r="F42">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <f t="shared" si="0"/>
-        <v>22009</v>
+        <f t="shared" si="1"/>
+        <v>21009</v>
       </c>
       <c r="B43">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C43">
         <v>9</v>
       </c>
       <c r="D43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E43">
         <v>4500</v>
       </c>
       <c r="F43">
-        <v>47055</v>
+        <v>47054</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <f t="shared" si="0"/>
-        <v>22010</v>
+        <f t="shared" si="1"/>
+        <v>21010</v>
       </c>
       <c r="B44">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C44">
         <v>10</v>
       </c>
       <c r="D44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E44">
         <v>5000</v>
       </c>
       <c r="F44">
+        <v>47054</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <f t="shared" si="1"/>
+        <v>22001</v>
+      </c>
+      <c r="B45">
+        <v>12</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45">
+        <v>11520</v>
+      </c>
+      <c r="F45">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <f t="shared" si="1"/>
+        <v>22002</v>
+      </c>
+      <c r="B46">
+        <v>12</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46">
+        <v>26880</v>
+      </c>
+      <c r="F46">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <f t="shared" si="1"/>
+        <v>22003</v>
+      </c>
+      <c r="B47">
+        <v>12</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47">
+        <v>42240</v>
+      </c>
+      <c r="F47">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <f t="shared" si="1"/>
+        <v>22004</v>
+      </c>
+      <c r="B48">
+        <v>12</v>
+      </c>
+      <c r="C48">
+        <v>4</v>
+      </c>
+      <c r="D48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48">
+        <v>59520</v>
+      </c>
+      <c r="F48">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <f t="shared" si="1"/>
+        <v>22005</v>
+      </c>
+      <c r="B49">
+        <v>12</v>
+      </c>
+      <c r="C49">
+        <v>5</v>
+      </c>
+      <c r="D49" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49">
+        <v>74880</v>
+      </c>
+      <c r="F49">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <f t="shared" si="1"/>
+        <v>22006</v>
+      </c>
+      <c r="B50">
+        <v>12</v>
+      </c>
+      <c r="C50">
+        <v>6</v>
+      </c>
+      <c r="D50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50">
+        <v>97920</v>
+      </c>
+      <c r="F50">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <f t="shared" si="1"/>
+        <v>22007</v>
+      </c>
+      <c r="B51">
+        <v>12</v>
+      </c>
+      <c r="C51">
+        <v>7</v>
+      </c>
+      <c r="D51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51">
+        <v>120960</v>
+      </c>
+      <c r="F51">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <f t="shared" si="1"/>
+        <v>22008</v>
+      </c>
+      <c r="B52">
+        <v>12</v>
+      </c>
+      <c r="C52">
+        <v>8</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52">
+        <v>142080</v>
+      </c>
+      <c r="F52">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <f t="shared" si="1"/>
+        <v>22009</v>
+      </c>
+      <c r="B53">
+        <v>12</v>
+      </c>
+      <c r="C53">
+        <v>9</v>
+      </c>
+      <c r="D53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53">
+        <v>174720</v>
+      </c>
+      <c r="F53">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <f t="shared" si="1"/>
+        <v>22010</v>
+      </c>
+      <c r="B54">
+        <v>12</v>
+      </c>
+      <c r="C54">
+        <v>10</v>
+      </c>
+      <c r="D54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54">
+        <v>205440</v>
+      </c>
+      <c r="F54">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <f t="shared" ref="A55:A64" si="2">10000+C55+B55*1000</f>
+        <v>22011</v>
+      </c>
+      <c r="B55">
+        <v>12</v>
+      </c>
+      <c r="C55">
+        <v>11</v>
+      </c>
+      <c r="D55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55">
+        <v>238080</v>
+      </c>
+      <c r="F55">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <f t="shared" si="2"/>
+        <v>22012</v>
+      </c>
+      <c r="B56">
+        <v>12</v>
+      </c>
+      <c r="C56">
+        <v>12</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56">
+        <v>282240</v>
+      </c>
+      <c r="F56">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <f t="shared" si="2"/>
+        <v>22013</v>
+      </c>
+      <c r="B57">
+        <v>12</v>
+      </c>
+      <c r="C57">
+        <v>13</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57">
+        <v>326400</v>
+      </c>
+      <c r="F57">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58">
+        <f t="shared" si="2"/>
+        <v>22014</v>
+      </c>
+      <c r="B58">
+        <v>12</v>
+      </c>
+      <c r="C58">
+        <v>14</v>
+      </c>
+      <c r="D58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58">
+        <v>370560</v>
+      </c>
+      <c r="F58">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <f t="shared" si="2"/>
+        <v>22015</v>
+      </c>
+      <c r="B59">
+        <v>12</v>
+      </c>
+      <c r="C59">
+        <v>15</v>
+      </c>
+      <c r="D59" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59">
+        <v>432000</v>
+      </c>
+      <c r="F59">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60">
+        <f t="shared" si="2"/>
+        <v>22016</v>
+      </c>
+      <c r="B60">
+        <v>12</v>
+      </c>
+      <c r="C60">
+        <v>16</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60">
+        <v>493440</v>
+      </c>
+      <c r="F60">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61">
+        <f t="shared" si="2"/>
+        <v>22017</v>
+      </c>
+      <c r="B61">
+        <v>12</v>
+      </c>
+      <c r="C61">
+        <v>17</v>
+      </c>
+      <c r="D61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61">
+        <v>556800</v>
+      </c>
+      <c r="F61">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62">
+        <f t="shared" si="2"/>
+        <v>22018</v>
+      </c>
+      <c r="B62">
+        <v>12</v>
+      </c>
+      <c r="C62">
+        <v>18</v>
+      </c>
+      <c r="D62" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62">
+        <v>643200</v>
+      </c>
+      <c r="F62">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63">
+        <f t="shared" si="2"/>
+        <v>22019</v>
+      </c>
+      <c r="B63">
+        <v>12</v>
+      </c>
+      <c r="C63">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63">
+        <v>729600</v>
+      </c>
+      <c r="F63">
+        <v>47055</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
+        <f t="shared" si="2"/>
+        <v>22020</v>
+      </c>
+      <c r="B64">
+        <v>12</v>
+      </c>
+      <c r="C64">
+        <v>20</v>
+      </c>
+      <c r="D64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64">
+        <v>816000</v>
+      </c>
+      <c r="F64">
         <v>47055</v>
       </c>
     </row>
